--- a/input_files/dangerous_products.xlsx
+++ b/input_files/dangerous_products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alon\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2fcf9ad746f2b86b/מסמכים/dormeco-sorting-script/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0055A0EC-7E4E-4F5A-AEF3-BCD8223AB2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ספירות מלאי של דורמקו 2025" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ספירות מלאי של דורמקו 2025'!$A$1:$C$37</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -254,7 +267,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -262,7 +275,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -270,7 +283,7 @@
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Times New Roman"/>
+      <name val="Aptos Display"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="major"/>
@@ -279,7 +292,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -288,7 +301,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -297,7 +310,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -305,7 +318,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -313,7 +326,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -321,7 +334,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -329,7 +342,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -338,7 +351,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -347,7 +360,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -355,7 +368,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -364,7 +377,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -372,7 +385,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -381,7 +394,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -390,7 +403,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -398,7 +411,7 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
